--- a/raw_data/results_csv/parser_v0.1.5/copa_cordillera_argentina_2026/parsed_results_v0_1_5.xlsx
+++ b/raw_data/results_csv/parser_v0.1.5/copa_cordillera_argentina_2026/parsed_results_v0_1_5.xlsx
@@ -80452,7 +80452,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Muchut Moyano, Rocíío Alumineí</t>
+          <t>Muchut Moyano, Rocío Alumineí</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -80495,7 +80495,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Loípez, Diane</t>
+          <t>López, Diane</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -80538,7 +80538,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Faríías, Tiare</t>
+          <t>Farías, Tiare</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -81785,7 +81785,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Gonzalez, Nicolas Agustíín</t>
+          <t>Gonzalez, Nicolas Agustín</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -81871,7 +81871,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Caro P, Cristoíbal Fdo</t>
+          <t>Caro P, Cristóbal Fdo</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -81914,7 +81914,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Flores, Joseí Luis</t>
+          <t>Flores, José Luis</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -81957,7 +81957,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Parra SM, Nicolaís</t>
+          <t>Parra SM, Nicolás</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -82000,7 +82000,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Becerra A., Martíín</t>
+          <t>Becerra A., Martín</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -82129,7 +82129,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Chacoín, Manuel</t>
+          <t>Chacón, Manuel</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -83677,7 +83677,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Cabello Tilleríía, Andre ís</t>
+          <t>Cabello Tillería, Andrés</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -83763,7 +83763,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Guinñazu, Selene</t>
+          <t>Guiñazu, Selene</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -84580,7 +84580,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Caro, Martíín</t>
+          <t>Caro, Martín</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -84666,7 +84666,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Bolanños, Kleiber</t>
+          <t>Bolaños, Kleiber</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -88295,7 +88295,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Muchut Moyano, Rocíío Alumineí</t>
+          <t>Muchut Moyano, Rocío Alumineí</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -88340,7 +88340,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Loípez, Diane</t>
+          <t>López, Diane</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -88385,7 +88385,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Faríías, Tiare</t>
+          <t>Farías, Tiare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -89690,7 +89690,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gonzalez, Nicolas Agustíín</t>
+          <t>Gonzalez, Nicolas Agustín</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -89780,7 +89780,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Caro P, Cristoíbal Fdo</t>
+          <t>Caro P, Cristóbal Fdo</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -89825,7 +89825,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Flores, Joseí Luis</t>
+          <t>Flores, José Luis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -89870,7 +89870,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parra SM, Nicolaís</t>
+          <t>Parra SM, Nicolás</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -89915,7 +89915,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Becerra A., Martíín</t>
+          <t>Becerra A., Martín</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -90050,7 +90050,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chacoín, Manuel</t>
+          <t>Chacón, Manuel</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -91670,7 +91670,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cabello Tilleríía, Andre ís</t>
+          <t>Cabello Tillería, Andrés</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -91760,7 +91760,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Guinñazu, Selene</t>
+          <t>Guiñazu, Selene</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -92615,7 +92615,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Caro, Martíín</t>
+          <t>Caro, Martín</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -92705,7 +92705,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bolanños, Kleiber</t>
+          <t>Bolaños, Kleiber</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
